--- a/assets/constructions/examples/ctd_ds4.xlsx
+++ b/assets/constructions/examples/ctd_ds4.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE6"/>
+  <dimension ref="A1:AJ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -584,11 +584,36 @@
           <t>adintws</t>
         </is>
       </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2301-3732-A1 11Р3АМ2 ГОСТ 10903-77</t>
+          <t>2301-4029-A1 ЭП342 ГОСТ 2092-77</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -604,15 +629,15 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>49</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>122</v>
+        <v>147.6</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
@@ -622,7 +647,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>11Р3АМ2</t>
+          <t>ЭП342</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -633,33 +658,33 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>ГОСТ 10903-77</t>
+          <t>ГОСТ 2092-77</t>
         </is>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>149</v>
+        <v>80</v>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
         <v>118</v>
       </c>
       <c r="T2" t="n">
-        <v>14.721</v>
+        <v>2.614</v>
       </c>
       <c r="U2" t="n">
-        <v>369</v>
+        <v>245</v>
       </c>
       <c r="V2" t="n">
-        <v>354.279</v>
+        <v>242.386</v>
       </c>
       <c r="W2" t="n">
-        <v>220</v>
+        <v>165</v>
       </c>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
@@ -673,7 +698,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>HSS</t>
+          <t>PME</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -683,19 +708,30 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>MKG_L:4</t>
+          <t>MKG_L:1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
           <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>PS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2301-3095 Р9К3 ГОСТ 10903-77</t>
+          <t>2301-4128-A1 11Р3АМ3Ф2 ГОСТ 2092-77</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -706,20 +742,20 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KMN</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>49</v>
+        <v>23.5</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>122</v>
+        <v>193</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
@@ -729,7 +765,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Р9К3</t>
+          <t>11Р3АМ3Ф2</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -740,33 +776,33 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>ГОСТ 10903-77</t>
+          <t>ГОСТ 2092-77</t>
         </is>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>187</v>
+        <v>120</v>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
         <v>118</v>
       </c>
       <c r="T3" t="n">
-        <v>14.721</v>
+        <v>7.06</v>
       </c>
       <c r="U3" t="n">
-        <v>407</v>
+        <v>360</v>
       </c>
       <c r="V3" t="n">
-        <v>392.279</v>
+        <v>352.94</v>
       </c>
       <c r="W3" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
@@ -785,24 +821,35 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>MKG_L:5</t>
+          <t>MKG_L:3</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
           <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>PMS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2301-4018-A1 Р6М5 ГОСТ 2092-77</t>
+          <t>2301-3438 ЭП342 ГОСТ 12121-77</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -813,20 +860,20 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PNK</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>7.7</v>
+        <v>13.9</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>144.6</v>
+        <v>114.2</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
@@ -836,7 +883,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Р6М5</t>
+          <t>ЭП342</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -847,7 +894,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>ГОСТ 2092-77</t>
+          <t>ГОСТ 12121-77</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -857,23 +904,23 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
         <v>118</v>
       </c>
       <c r="T4" t="n">
-        <v>2.313</v>
+        <v>4.176</v>
       </c>
       <c r="U4" t="n">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="V4" t="n">
-        <v>237.687</v>
+        <v>218.824</v>
       </c>
       <c r="W4" t="n">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
@@ -887,12 +934,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>HSS</t>
+          <t>PME</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -903,58 +950,71 @@
       <c r="AE4" t="inlineStr">
         <is>
           <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>PS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2301-0036 Р6М3 ГОСТ 10903-77 с парооксидированием</t>
+          <t>A4247-12.5</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ТИЗ</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>WALTER</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>A4247</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>KM</t>
-        </is>
-      </c>
+          <t>PMKNS</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>71</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>82.25</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6.58</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Р6М3</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>HSS-E</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>VAP</t>
+          <t>Vap</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>ГОСТ 10903-77</t>
+          <t>DIN 345</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -966,21 +1026,25 @@
       <c r="Q5" t="n">
         <v>81</v>
       </c>
-      <c r="R5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Alpha XE</t>
+        </is>
+      </c>
       <c r="S5" t="n">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="T5" t="n">
-        <v>3.455</v>
+        <v>2.914</v>
       </c>
       <c r="U5" t="n">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="V5" t="n">
-        <v>171.545</v>
+        <v>179.086</v>
       </c>
       <c r="W5" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
@@ -989,7 +1053,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019 / Каталог инструмента ОПН</t>
+          <t>2015 / Walter-tools Website</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -999,7 +1063,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>h8</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1010,13 +1074,24 @@
       <c r="AE5" t="inlineStr">
         <is>
           <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2301-0020 Р3М3 ГОСТ 10903-77 с парооксидированием</t>
+          <t>2301-3377 Р18 ГОСТ 12121-77 с парооксидированием</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1027,20 +1102,20 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>PMKS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>58</v>
+        <v>83.2</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
@@ -1050,7 +1125,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Р3М3</t>
+          <t>Р18</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -1061,7 +1136,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>ГОСТ 10903-77</t>
+          <t>ГОСТ 12121-77</t>
         </is>
       </c>
       <c r="O6" t="n">
@@ -1078,16 +1153,16 @@
         <v>118</v>
       </c>
       <c r="T6" t="n">
-        <v>2.554</v>
+        <v>2.524</v>
       </c>
       <c r="U6" t="n">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="V6" t="n">
-        <v>153.446</v>
+        <v>178.476</v>
       </c>
       <c r="W6" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
@@ -1117,6 +1192,17 @@
       <c r="AE6" t="inlineStr">
         <is>
           <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
         </is>
       </c>
     </row>
